--- a/PR. Final Project.xlsx
+++ b/PR. Final Project.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\AppData\Local\Packages\5319275A.WhatsAppDesktop_cv1g1gvanyjgm\LocalState\sessions\FE12AEB988419FBFA1C8AF7544967084637E1C78\transfers\2026-22\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\Excel_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D50FFFF3-719C-4EE0-B812-225AB34B7EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763AE8B1-2500-499C-9353-D735DDFEAC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2373" uniqueCount="478">
   <si>
     <t>Transaction_ID</t>
   </si>
@@ -1471,18 +1471,6 @@
     <t>Sum of Total_Amount</t>
   </si>
   <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>Qtr2</t>
-  </si>
-  <si>
-    <t>Qtr3</t>
-  </si>
-  <si>
     <t>Best Region</t>
   </si>
   <si>
@@ -1837,7 +1825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1935,9 +1923,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1973,6 +1958,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2015,202 +2003,341 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="69">
+  <dxfs count="54">
     <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center"/>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -2645,335 +2772,22 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3355,23 +3169,47 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Pivot_Analysis!$A$4:$A$5</c:f>
+              <c:f>Pivot_Analysis!$A$4:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_Analysis!$B$4:$B$5</c:f>
+              <c:f>Pivot_Analysis!$B$4:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>"₹"\ #,##0.00</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1119.8399999999999</c:v>
+                  <c:v>13489.69</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13329.499999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10309.64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8749.6200000000008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1349.89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3454,6 +3292,20 @@
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="&quot;₹&quot;\ #,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -3939,7 +3791,8 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1">
-                  <a:tint val="65000"/>
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -3961,7 +3814,8 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1">
-                  <a:tint val="30000"/>
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -3983,7 +3837,7 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1">
-                  <a:tint val="60000"/>
+                  <a:tint val="65000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -4057,10 +3911,16 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Pivot_Analysis!$E$4:$E$5</c:f>
+              <c:f>Pivot_Analysis!$E$4:$E$7</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Appliances</c:v>
                 </c:pt>
               </c:strCache>
@@ -4068,12 +3928,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_Analysis!$F$4:$F$5</c:f>
+              <c:f>Pivot_Analysis!$F$4:$F$7</c:f>
               <c:numCache>
                 <c:formatCode>"₹"\ #,##0.00</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1119.8399999999999</c:v>
+                  <c:v>34589.120000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10699.499999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1939.72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4474,7 +4340,7 @@
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -4583,13 +4449,13 @@
                 <c:formatCode>"₹"\ #,##0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>179.97</c:v>
+                  <c:v>15459.349999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>379.94</c:v>
+                  <c:v>15609.599999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>559.92999999999995</c:v>
+                  <c:v>16159.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4610,7 +4476,6 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
         <c:axId val="1049002175"/>
         <c:axId val="1049000255"/>
       </c:barChart>
@@ -4620,7 +4485,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -4671,7 +4536,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:numFmt formatCode="&quot;₹&quot;\ #,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -4774,944 +4639,6 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[PR. Final Project.xlsx]Pivot_Analysis!PivotTable4</c:name>
-    <c:fmtId val="9"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-IN" sz="1600" b="1" i="0" u="none" strike="noStrike" baseline="0">
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>Monthly Trend</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US">
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:endParaRPr>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln w="34925" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-1.2112632400889514E-2"/>
-              <c:y val="-9.487277631962672E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:dLblPos val="r"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-3.4084076924146875E-2"/>
-              <c:y val="-8.5613517060367447E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:dLblPos val="r"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-3.9130758730858965E-2"/>
-              <c:y val="-0.10413203557888606"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:dLblPos val="r"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-4.2915770085892938E-2"/>
-              <c:y val="-7.1724628171478566E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:dLblPos val="r"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln w="34925" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="6"/>
-        <c:spPr>
-          <a:ln w="34925" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot_Analysis!$F$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="34925" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Pivot_Analysis!$E$16:$E$21</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="3"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Qtr2</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Qtr3</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Qtr2</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2024</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>2025</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot_Analysis!$F$16:$F$21</c:f>
-              <c:numCache>
-                <c:formatCode>"₹"\ #,##0.00</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>439.92999999999995</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>439.94</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>239.97</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4C98-46A7-80CA-3511C57005DD}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:upDownBars>
-          <c:gapWidth val="150"/>
-          <c:upBars>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="15000"/>
-                    <a:lumOff val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:upBars>
-          <c:downBars>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:downBars>
-        </c:upDownBars>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1048950815"/>
-        <c:axId val="1048957055"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1048950815"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1048957055"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1048957055"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="&quot;₹&quot;\ #,##0.00" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1048950815"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill>
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="74000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="45000"/>
-            <a:lumOff val="55000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="83000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="45000"/>
-            <a:lumOff val="55000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="30000"/>
-            <a:lumOff val="70000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:lin ang="5400000" scaled="1"/>
-    </a:gradFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5938,23 +4865,47 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Pivot_Analysis!$A$4:$A$5</c:f>
+              <c:f>Pivot_Analysis!$A$4:$A$9</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
+                  <c:v>South</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>North</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>East</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Central</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_Analysis!$B$4:$B$5</c:f>
+              <c:f>Pivot_Analysis!$B$4:$B$9</c:f>
               <c:numCache>
                 <c:formatCode>"₹"\ #,##0.00</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>1119.8399999999999</c:v>
+                  <c:v>13489.69</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>13329.499999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10309.64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8749.6200000000008</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1349.89</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6152,7 +5103,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6361,7 +5312,7 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1">
-                  <a:tint val="65000"/>
+                  <a:shade val="65000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -6382,9 +5333,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1">
-                  <a:tint val="30000"/>
-                </a:schemeClr>
+                <a:schemeClr val="accent1"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -6405,7 +5354,7 @@
             <c:spPr>
               <a:solidFill>
                 <a:schemeClr val="accent1">
-                  <a:tint val="60000"/>
+                  <a:tint val="65000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln w="19050">
@@ -6479,10 +5428,16 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Pivot_Analysis!$E$4:$E$5</c:f>
+              <c:f>Pivot_Analysis!$E$4:$E$7</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>Electronics</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Furniture</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Appliances</c:v>
                 </c:pt>
               </c:strCache>
@@ -6490,12 +5445,18 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Pivot_Analysis!$F$4:$F$5</c:f>
+              <c:f>Pivot_Analysis!$F$4:$F$7</c:f>
               <c:numCache>
                 <c:formatCode>"₹"\ #,##0.00</c:formatCode>
-                <c:ptCount val="1"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>1119.8399999999999</c:v>
+                  <c:v>34589.120000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10699.499999999996</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1939.72</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6643,7 +5604,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6662,31 +5623,6 @@
   </c:pivotSource>
   <c:chart>
     <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-IN"/>
-              <a:t>Revenue by Customer Segment</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6779,7 +5715,7 @@
     <c:plotArea>
       <c:layout/>
       <c:barChart>
-        <c:barDir val="col"/>
+        <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
@@ -6888,13 +5824,13 @@
                 <c:formatCode>"₹"\ #,##0.00</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>179.97</c:v>
+                  <c:v>15459.349999999997</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>379.94</c:v>
+                  <c:v>15609.599999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>559.92999999999995</c:v>
+                  <c:v>16159.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6915,7 +5851,6 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
         <c:axId val="1049002175"/>
         <c:axId val="1049000255"/>
       </c:barChart>
@@ -6925,7 +5860,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="b"/>
+        <c:axPos val="l"/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -6976,7 +5911,7 @@
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
-        <c:axPos val="l"/>
+        <c:axPos val="b"/>
         <c:numFmt formatCode="&quot;₹&quot;\ #,##0.00" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -6985,584 +5920,14 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill>
-      <a:gsLst>
-        <a:gs pos="0">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="74000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="45000"/>
-            <a:lumOff val="55000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="83000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="45000"/>
-            <a:lumOff val="55000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="100000">
-          <a:schemeClr val="accent1">
-            <a:lumMod val="30000"/>
-            <a:lumOff val="70000"/>
-          </a:schemeClr>
-        </a:gs>
-      </a:gsLst>
-      <a:lin ang="5400000" scaled="1"/>
-    </a:gradFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[PR. Final Project.xlsx]Pivot_Analysis!PivotTable4</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:ln w="34925" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-1.2112632400889514E-2"/>
-              <c:y val="-9.487277631962672E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:dLblPos val="r"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-3.4084076924146875E-2"/>
-              <c:y val="-8.5613517060367447E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:dLblPos val="r"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-3.9130758730858965E-2"/>
-              <c:y val="-0.10413203557888606"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:dLblPos val="r"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:layout>
-            <c:manualLayout>
-              <c:x val="-4.2915770085892938E-2"/>
-              <c:y val="-7.1724628171478566E-2"/>
-            </c:manualLayout>
-          </c:layout>
-          <c:dLblPos val="r"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Pivot_Analysis!$F$15</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="34925" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:gradFill rotWithShape="1">
-                <a:gsLst>
-                  <a:gs pos="0">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="103000"/>
-                      <a:lumMod val="102000"/>
-                      <a:tint val="94000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="50000">
-                    <a:schemeClr val="accent1">
-                      <a:satMod val="110000"/>
-                      <a:lumMod val="100000"/>
-                      <a:shade val="100000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="accent1">
-                      <a:lumMod val="99000"/>
-                      <a:satMod val="120000"/>
-                      <a:shade val="78000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst>
-                <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                  <a:srgbClr val="000000">
-                    <a:alpha val="63000"/>
-                  </a:srgbClr>
-                </a:outerShdw>
-              </a:effectLst>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:multiLvlStrRef>
-              <c:f>Pivot_Analysis!$E$16:$E$21</c:f>
-              <c:multiLvlStrCache>
-                <c:ptCount val="3"/>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>Qtr2</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>Qtr3</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>Qtr2</c:v>
-                  </c:pt>
-                </c:lvl>
-                <c:lvl>
-                  <c:pt idx="0">
-                    <c:v>2024</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>2025</c:v>
-                  </c:pt>
-                </c:lvl>
-              </c:multiLvlStrCache>
-            </c:multiLvlStrRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Pivot_Analysis!$F$16:$F$21</c:f>
-              <c:numCache>
-                <c:formatCode>"₹"\ #,##0.00</c:formatCode>
-                <c:ptCount val="3"/>
-                <c:pt idx="0">
-                  <c:v>439.92999999999995</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>439.94</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>239.97</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1520-46D0-8D74-6ACE87519EB2}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:upDownBars>
-          <c:gapWidth val="150"/>
-          <c:upBars>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="15000"/>
-                    <a:lumOff val="85000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:upBars>
-          <c:downBars>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:downBars>
-        </c:upDownBars>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1048950815"/>
-        <c:axId val="1048957055"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1048950815"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7574,10 +5939,10 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr rtl="0">
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
@@ -7593,42 +5958,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1048957055"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1048957055"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="&quot;₹&quot;\ #,##0.00" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1048950815"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+      </c:dTable>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -7849,92 +6179,12 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="14">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -9500,508 +7750,6 @@
 </file>
 
 <file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -10504,7 +8252,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11023,7 +8771,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -11526,508 +9274,6 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="342">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx2"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="34925" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="3"/>
-    <cs:effectRef idx="3"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1600" b="1" kern="1200" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
@@ -12161,7 +9407,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>₹ 0.00</a:t>
+            <a:t>₹ 47,228.34</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1600" b="1">
             <a:solidFill>
@@ -12242,7 +9488,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>North</a:t>
+            <a:t>South</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1600" b="1">
             <a:solidFill>
@@ -12323,7 +9569,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
             <a:pPr algn="ctr"/>
-            <a:t>Appliances</a:t>
+            <a:t>Electronics</a:t>
           </a:fld>
           <a:endParaRPr lang="en-IN" sz="1600" b="1">
             <a:solidFill>
@@ -12502,10 +9748,10 @@
       <xdr:rowOff>161192</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>217715</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>102576</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>384342</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>133685</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -12532,52 +9778,14 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>497632</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>124408</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>108857</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="11" name="Chart 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{72CCD253-9251-4D82-B4F1-A341C72F7FB6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>125557</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>49549</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1454727" cy="1801091"/>
+    <xdr:ext cx="1454727" cy="1932421"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:graphicFrame macro="">
@@ -12612,8 +9820,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="47625" y="1078057"/>
-              <a:ext cx="1454727" cy="1801091"/>
+              <a:off x="0" y="1971260"/>
+              <a:ext cx="1454727" cy="1932421"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -12647,7 +9855,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>64943</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1439333" cy="1570181"/>
@@ -12685,7 +9893,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="31750" y="3557443"/>
+              <a:off x="31750" y="4192443"/>
               <a:ext cx="1439333" cy="1570181"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12719,9 +9927,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>31750</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>34637</xdr:rowOff>
+      <xdr:colOff>70234</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>34638</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1422400" cy="1472046"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -12758,7 +9966,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="31750" y="5622637"/>
+              <a:off x="70234" y="6000296"/>
               <a:ext cx="1422400" cy="1472046"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -12869,22 +10077,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>59766</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>15875</xdr:rowOff>
+      <xdr:rowOff>38485</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>873125</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>24536</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>382407</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>57727</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15">
+        <xdr:cNvPr id="8" name="Picture 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69FA84A0-B5A2-740A-E9B5-6AF675D746B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80A3B305-81C9-282F-928B-C3823F7ECFC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -12893,29 +10101,19 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="59766" y="15875"/>
-          <a:ext cx="1432484" cy="1215161"/>
+          <a:off x="0" y="38485"/>
+          <a:ext cx="1883316" cy="1635606"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="00B050"/>
-        </a:solidFill>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -13028,42 +10226,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>327660</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>297180</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AE6FFC0-53F6-5155-7F4D-074E0834795B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -18083,8 +15245,501 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7326867A-5E29-4E84-832C-1DE91DFB9F6F}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" rowHeaderCaption="Date">
-  <location ref="E15:F21" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FF1BBDB3-E502-4CC8-8941-042EBC156A3F}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="29" rowHeaderCaption="Category">
+  <location ref="E3:F7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="14" showAll="0">
+      <items count="163">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="15">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total_Amount" fld="15" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="12">
+    <format dxfId="29">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="28">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="27">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="24">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+    <format dxfId="23">
+      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="22">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+    <format dxfId="21">
+      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    </format>
+    <format dxfId="20">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="18">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="12">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="6" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="15" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="45474"/>
+            <customFilter operator="lessThanOrEqual" val="45565"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59318459-FE68-41C8-B38A-35DCEB4138D2}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Region">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
     <pivotField numFmtId="14" showAll="0">
@@ -18261,23 +15916,32 @@
     <pivotField showAll="0">
       <items count="4">
         <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField numFmtId="1" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" x="4"/>
+        <item x="0"/>
+        <item x="4"/>
         <item x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="3"/>
+        <item x="1"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
     </pivotField>
     <pivotField showAll="0">
       <items count="4">
@@ -18291,66 +15955,64 @@
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="15">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
-        <item sd="0" x="6"/>
-        <item sd="0" x="7"/>
-        <item sd="0" x="8"/>
-        <item sd="0" x="9"/>
-        <item sd="0" x="10"/>
-        <item sd="0" x="11"/>
-        <item sd="0" x="12"/>
-        <item sd="0" x="13"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="7">
-        <item sd="0" x="0"/>
-        <item sd="0" x="1"/>
-        <item sd="0" x="2"/>
-        <item sd="0" x="3"/>
-        <item sd="0" x="4"/>
-        <item sd="0" x="5"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" showAll="0">
+    <pivotField showAll="0">
       <items count="5">
-        <item sd="0" x="0"/>
+        <item x="0"/>
         <item x="1"/>
         <item x="2"/>
-        <item sd="0" x="3"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
   </pivotFields>
-  <rowFields count="3">
-    <field x="18"/>
-    <field x="17"/>
-    <field x="16"/>
+  <rowFields count="1">
+    <field x="10"/>
   </rowFields>
   <rowItems count="6">
     <i>
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
       <x v="3"/>
     </i>
     <i>
       <x v="2"/>
     </i>
-    <i r="1">
-      <x v="2"/>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -18362,87 +16024,53 @@
   <dataFields count="1">
     <dataField name="Sum of Total_Amount" fld="15" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
-  <formats count="15">
-    <format dxfId="0">
+  <formats count="12">
+    <format dxfId="41">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="40">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
-      <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    <format dxfId="39">
+      <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="18" count="2">
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
+          <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="4">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="36">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="35">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="34">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
-      <pivotArea field="18" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
+    <format dxfId="33">
+      <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
-          <reference field="18" count="2">
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
+          <reference field="10" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="30">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="12">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="18" count="1">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="13">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="18" count="1">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="14">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="18" count="2">
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
   </formats>
-  <chartFormats count="6">
+  <chartFormats count="2">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -18452,67 +16080,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="16" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-          <reference field="18" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="16" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-          <reference field="18" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="16" count="1" selected="0">
-            <x v="11"/>
-          </reference>
-          <reference field="18" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="3">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="16" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-          <reference field="18" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="9" format="6" series="1">
+    <chartFormat chart="5" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -18523,6 +16091,23 @@
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="15" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="45474"/>
+            <customFilter operator="lessThanOrEqual" val="45565"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -18534,7 +16119,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D7043D17-899B-4168-82AF-691B8571AD01}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4" rowHeaderCaption="Customer_Segment">
   <location ref="A15:B19" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -18713,8 +16298,8 @@
     <pivotField showAll="0">
       <items count="4">
         <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
+        <item x="0"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18723,11 +16308,11 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" x="4"/>
+        <item x="0"/>
+        <item x="4"/>
         <item x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="3"/>
+        <item x="1"/>
+        <item x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18816,48 +16401,48 @@
     <dataField name="Sum of Total_Amount" fld="15" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="15">
+    <format dxfId="53">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="52">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="51">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="50">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="49">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="48">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="47">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="46">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="45">
       <pivotArea field="11" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="24">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="11" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -18882,829 +16467,23 @@
     </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FF1BBDB3-E502-4CC8-8941-042EBC156A3F}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="29" rowHeaderCaption="Category">
-  <location ref="E3:F5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="163">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="4">
-        <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" x="4"/>
-        <item x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="6"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total_Amount" fld="15" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="27">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="28">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="29">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="30">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="32">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="33">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="34">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="35">
-      <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="36">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="6" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="37">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="38">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="12">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="1" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="16" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="5" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="17" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="6" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{59318459-FE68-41C8-B38A-35DCEB4138D2}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="5" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="9" rowHeaderCaption="Region">
-  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="14" showAll="0">
-      <items count="163">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item x="100"/>
-        <item x="101"/>
-        <item x="102"/>
-        <item x="103"/>
-        <item x="104"/>
-        <item x="105"/>
-        <item x="106"/>
-        <item x="107"/>
-        <item x="108"/>
-        <item x="109"/>
-        <item x="110"/>
-        <item x="111"/>
-        <item x="112"/>
-        <item x="113"/>
-        <item x="114"/>
-        <item x="115"/>
-        <item x="116"/>
-        <item x="117"/>
-        <item x="118"/>
-        <item x="119"/>
-        <item x="120"/>
-        <item x="121"/>
-        <item x="122"/>
-        <item x="123"/>
-        <item x="124"/>
-        <item x="125"/>
-        <item x="126"/>
-        <item x="127"/>
-        <item x="128"/>
-        <item x="129"/>
-        <item x="130"/>
-        <item x="131"/>
-        <item x="132"/>
-        <item x="133"/>
-        <item x="134"/>
-        <item x="135"/>
-        <item x="136"/>
-        <item x="137"/>
-        <item x="138"/>
-        <item x="139"/>
-        <item x="140"/>
-        <item x="141"/>
-        <item x="142"/>
-        <item x="143"/>
-        <item x="144"/>
-        <item x="145"/>
-        <item x="146"/>
-        <item x="147"/>
-        <item x="148"/>
-        <item x="149"/>
-        <item x="150"/>
-        <item x="151"/>
-        <item x="152"/>
-        <item x="153"/>
-        <item x="154"/>
-        <item x="155"/>
-        <item x="156"/>
-        <item x="157"/>
-        <item x="158"/>
-        <item x="159"/>
-        <item x="160"/>
-        <item x="161"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="6">
-        <item h="1" x="0"/>
-        <item h="1" x="4"/>
-        <item x="2"/>
-        <item h="1" x="1"/>
-        <item h="1" x="3"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField dataField="1" numFmtId="164" showAll="0"/>
-    <pivotField showAll="0">
-      <items count="15">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="10"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total_Amount" fld="15" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="12">
-    <format dxfId="39">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="40">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="41">
-      <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="42">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="10" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="43">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="44">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-    <format dxfId="45">
-      <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="46">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-    <format dxfId="47">
-      <pivotArea field="10" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
-    </format>
-    <format dxfId="48">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="10" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="49">
-      <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="50">
-      <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="1" type="dateBetween" evalOrder="-1" id="15" name="Date">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <customFilters and="1">
+            <customFilter operator="greaterThanOrEqual" val="45474"/>
+            <customFilter operator="lessThanOrEqual" val="45565"/>
+          </customFilters>
+        </filterColumn>
+      </autoFilter>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{0605FD5F-26C8-4aeb-8148-2DB25E43C511}">
+          <x15:pivotFilter useWholeDay="1"/>
+        </ext>
+      </extLst>
+    </filter>
+  </filters>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
@@ -19722,14 +16501,13 @@
     <pivotTable tabId="15" name="PivotTable1"/>
     <pivotTable tabId="15" name="PivotTable2"/>
     <pivotTable tabId="15" name="PivotTable3"/>
-    <pivotTable tabId="15" name="PivotTable4"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1971773177">
       <items count="3">
         <i x="1" s="1"/>
-        <i x="0"/>
-        <i x="2"/>
+        <i x="0" s="1"/>
+        <i x="2" s="1"/>
       </items>
     </tabular>
   </data>
@@ -19742,16 +16520,15 @@
     <pivotTable tabId="15" name="PivotTable1"/>
     <pivotTable tabId="15" name="PivotTable2"/>
     <pivotTable tabId="15" name="PivotTable3"/>
-    <pivotTable tabId="15" name="PivotTable4"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1971773177">
       <items count="5">
-        <i x="0"/>
-        <i x="4"/>
+        <i x="0" s="1"/>
+        <i x="4" s="1"/>
         <i x="2" s="1"/>
-        <i x="1"/>
-        <i x="3"/>
+        <i x="1" s="1"/>
+        <i x="3" s="1"/>
       </items>
     </tabular>
   </data>
@@ -19764,7 +16541,6 @@
     <pivotTable tabId="15" name="PivotTable1"/>
     <pivotTable tabId="15" name="PivotTable2"/>
     <pivotTable tabId="15" name="PivotTable3"/>
-    <pivotTable tabId="15" name="PivotTable4"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1971773177">
@@ -19795,29 +16571,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14998D99-2DE0-4F1D-B48E-699D9461A1B7}" name="Table1" displayName="Table1" ref="A1:P251" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{14998D99-2DE0-4F1D-B48E-699D9461A1B7}" name="Table1" displayName="Table1" ref="A1:P251" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <autoFilter ref="A1:P251" xr:uid="{14998D99-2DE0-4F1D-B48E-699D9461A1B7}"/>
   <tableColumns count="16">
-    <tableColumn id="1" xr3:uid="{CF5D4738-4BBA-4A2C-9F94-C141BA80CBC9}" name="Transaction_ID" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{771EDCCE-7827-4226-A35D-D1205F55FF51}" name="Date" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{83CF8773-4C40-4793-8A24-D72B629E1ABF}" name="Customer_ID" dataDxfId="64"/>
-    <tableColumn id="4" xr3:uid="{B19ACD59-2783-4A8C-835D-C7CDA2D2AEF0}" name="Customer_Name" dataDxfId="63"/>
-    <tableColumn id="5" xr3:uid="{EA268F9E-050B-4E3D-BB66-AAE0BE60354B}" name="Product_ID" dataDxfId="62"/>
-    <tableColumn id="6" xr3:uid="{A0DB81C8-0DFC-4AC0-AD79-61723BD2EFD8}" name="Product_Name" dataDxfId="61"/>
-    <tableColumn id="7" xr3:uid="{0F6A0A47-DB76-4747-A0E0-5BFE20C2B034}" name="Category" dataDxfId="60"/>
-    <tableColumn id="8" xr3:uid="{BEC8B13C-6A03-404E-943C-6DF2B9A34A44}" name="Quantity" dataDxfId="59"/>
-    <tableColumn id="9" xr3:uid="{80BE7718-40C8-45E1-8139-8AF91719BC92}" name="Unit_Price" dataDxfId="58"/>
-    <tableColumn id="10" xr3:uid="{0D4E15D3-1BD7-4DDD-B332-C9C310C51A58}" name="Payment_Method" dataDxfId="57"/>
-    <tableColumn id="11" xr3:uid="{24642D2C-C8CF-4580-A239-E5E7E9526774}" name="Region" dataDxfId="56"/>
-    <tableColumn id="12" xr3:uid="{EFCBAF30-E334-42A2-8BA5-26F4DD657873}" name="Customer_Segment" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{068D8A2B-3C8A-4EEE-BF67-D37CC7B88036}" name="Customer_Since" dataDxfId="54"/>
-    <tableColumn id="16" xr3:uid="{76D6B772-A88B-4007-87FA-7FDF6D700DE1}" name="Customer_Tenure" dataDxfId="53">
+    <tableColumn id="1" xr3:uid="{CF5D4738-4BBA-4A2C-9F94-C141BA80CBC9}" name="Transaction_ID" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{771EDCCE-7827-4226-A35D-D1205F55FF51}" name="Date" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{83CF8773-4C40-4793-8A24-D72B629E1ABF}" name="Customer_ID" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{B19ACD59-2783-4A8C-835D-C7CDA2D2AEF0}" name="Customer_Name" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{EA268F9E-050B-4E3D-BB66-AAE0BE60354B}" name="Product_ID" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{A0DB81C8-0DFC-4AC0-AD79-61723BD2EFD8}" name="Product_Name" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{0F6A0A47-DB76-4747-A0E0-5BFE20C2B034}" name="Category" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{BEC8B13C-6A03-404E-943C-6DF2B9A34A44}" name="Quantity" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{80BE7718-40C8-45E1-8139-8AF91719BC92}" name="Unit_Price" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{0D4E15D3-1BD7-4DDD-B332-C9C310C51A58}" name="Payment_Method" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{24642D2C-C8CF-4580-A239-E5E7E9526774}" name="Region" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{EFCBAF30-E334-42A2-8BA5-26F4DD657873}" name="Customer_Segment" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{068D8A2B-3C8A-4EEE-BF67-D37CC7B88036}" name="Customer_Since" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{76D6B772-A88B-4007-87FA-7FDF6D700DE1}" name="Customer_Tenure" dataDxfId="2">
       <calculatedColumnFormula>DATEDIF(M2,TODAY(),"Y")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{E0A13D99-937A-479A-BBE6-9C677746E043}" name="Month_End_Date" dataDxfId="52">
+    <tableColumn id="17" xr3:uid="{E0A13D99-937A-479A-BBE6-9C677746E043}" name="Month_End_Date" dataDxfId="1">
       <calculatedColumnFormula>EOMONTH(Dataset!B2,0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{F6474BA8-B439-49B5-884A-F9F0D8D6168B}" name="Total_Amount" dataDxfId="51"/>
+    <tableColumn id="14" xr3:uid="{F6474BA8-B439-49B5-884A-F9F0D8D6168B}" name="Total_Amount" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -19826,42 +16602,42 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
-    <a:clrScheme name="Orange">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="637052"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="CCDDEA"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="E48312"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="BD582C"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="865640"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="9B8357"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C2BC80"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="94A088"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="2998E3"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="8C8C8C"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
@@ -20022,12 +16798,12 @@
 <file path=xl/timelineCaches/timelineCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <timelineCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="xr10" name="NativeTimeline_Date" xr10:uid="{AF9CB47C-386E-4BA6-8EBC-1249EC8AB78F}" sourceName="Date">
   <pivotTables>
-    <pivotTable tabId="15" name="PivotTable4"/>
     <pivotTable tabId="15" name="PivotTable1"/>
     <pivotTable tabId="15" name="PivotTable2"/>
     <pivotTable tabId="15" name="PivotTable3"/>
   </pivotTables>
-  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="1971773177" filterType="unknown">
+  <state minimalRefreshVersion="6" lastRefreshVersion="6" pivotCacheId="1971773177" filterType="dateBetween">
+    <selection startDate="2024-07-01T00:00:00" endDate="2024-09-30T00:00:00"/>
     <bounds startDate="2024-01-01T00:00:00" endDate="2026-01-01T00:00:00"/>
   </state>
 </timelineCacheDefinition>
@@ -20059,8 +16835,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A1" s="42"/>
-      <c r="B1" s="42"/>
+      <c r="A1" s="41"/>
+      <c r="B1" s="41"/>
       <c r="C1" s="57"/>
       <c r="D1" s="57"/>
       <c r="E1" s="57"/>
@@ -20078,13 +16854,13 @@
       <c r="Q1" s="57"/>
       <c r="R1" s="57"/>
       <c r="S1" s="57"/>
-      <c r="T1" s="42"/>
-      <c r="U1" s="42"/>
-      <c r="V1" s="42"/>
+      <c r="T1" s="41"/>
+      <c r="U1" s="41"/>
+      <c r="V1" s="41"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A2" s="42"/>
-      <c r="B2" s="42"/>
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
       <c r="C2" s="57"/>
       <c r="D2" s="57"/>
       <c r="E2" s="57"/>
@@ -20102,13 +16878,13 @@
       <c r="Q2" s="57"/>
       <c r="R2" s="57"/>
       <c r="S2" s="57"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="42"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A3" s="42"/>
-      <c r="B3" s="42"/>
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="57"/>
       <c r="D3" s="57"/>
       <c r="E3" s="57"/>
@@ -20126,13 +16902,13 @@
       <c r="Q3" s="57"/>
       <c r="R3" s="57"/>
       <c r="S3" s="57"/>
-      <c r="T3" s="42"/>
-      <c r="U3" s="42"/>
-      <c r="V3" s="42"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="41"/>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A4" s="42"/>
-      <c r="B4" s="42"/>
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="57"/>
       <c r="D4" s="57"/>
       <c r="E4" s="57"/>
@@ -20150,99 +16926,99 @@
       <c r="Q4" s="57"/>
       <c r="R4" s="57"/>
       <c r="S4" s="57"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="42"/>
-      <c r="V4" s="42"/>
+      <c r="T4" s="41"/>
+      <c r="U4" s="41"/>
+      <c r="V4" s="41"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A5" s="42"/>
-      <c r="B5" s="42"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="43"/>
-      <c r="M5" s="43"/>
-      <c r="N5" s="43"/>
-      <c r="O5" s="43"/>
-      <c r="P5" s="43"/>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="43"/>
-      <c r="T5" s="43"/>
-      <c r="U5" s="42"/>
-      <c r="V5" s="42"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="42"/>
+      <c r="M5" s="42"/>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="42"/>
+      <c r="T5" s="42"/>
+      <c r="U5" s="41"/>
+      <c r="V5" s="41"/>
     </row>
     <row r="6" spans="1:28" ht="20.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="42"/>
-      <c r="B6" s="42"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45" t="s">
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44" t="s">
         <v>411</v>
       </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45" t="s">
-        <v>466</v>
-      </c>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45" t="s">
-        <v>467</v>
-      </c>
-      <c r="L6" s="43"/>
-      <c r="M6" s="45" t="s">
-        <v>468</v>
-      </c>
-      <c r="N6" s="45"/>
-      <c r="O6" s="43"/>
-      <c r="P6" s="43"/>
-      <c r="Q6" s="43"/>
-      <c r="R6" s="43"/>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-      <c r="U6" s="42"/>
-      <c r="V6" s="42"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44" t="s">
+        <v>462</v>
+      </c>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44" t="s">
+        <v>463</v>
+      </c>
+      <c r="L6" s="42"/>
+      <c r="M6" s="44" t="s">
+        <v>464</v>
+      </c>
+      <c r="N6" s="44"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="41"/>
+      <c r="V6" s="41"/>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A7" s="42"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="42"/>
-      <c r="V7" s="42"/>
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="41"/>
+      <c r="V7" s="41"/>
       <c r="Y7" s="12">
         <f>Pivot_Analysis!B9</f>
-        <v>0</v>
+        <v>47228.340000000004</v>
       </c>
       <c r="Z7" t="str">
         <f>Pivot_Analysis!A4</f>
-        <v>North</v>
+        <v>South</v>
       </c>
       <c r="AA7" t="str">
         <f>Pivot_Analysis!E4</f>
-        <v>Appliances</v>
+        <v>Electronics</v>
       </c>
       <c r="AB7" t="str">
         <f>Pivot_Analysis!A18</f>
@@ -20250,1255 +17026,1255 @@
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="43"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="42"/>
-      <c r="V8" s="42"/>
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="41"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="43"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="43"/>
-      <c r="R9" s="43"/>
-      <c r="S9" s="43"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="42"/>
-      <c r="V9" s="42"/>
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="42"/>
+      <c r="L9" s="42"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="42"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="42"/>
+      <c r="Q9" s="42"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="41"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="43"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="43"/>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="43"/>
-      <c r="P10" s="43"/>
-      <c r="Q10" s="43"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="42"/>
-      <c r="V10" s="42"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="42"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="42"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="42"/>
+      <c r="T10" s="42"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="41"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A11" s="42"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="43"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="43"/>
-      <c r="P11" s="43"/>
-      <c r="Q11" s="43"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="42"/>
-      <c r="V11" s="42"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="42"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="42"/>
+      <c r="L11" s="42"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="42"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="42"/>
+      <c r="Q11" s="42"/>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="41"/>
+      <c r="V11" s="41"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="43"/>
-      <c r="P12" s="43"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="42"/>
-      <c r="V12" s="42"/>
+      <c r="A12" s="41"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="42"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="42"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="42"/>
+      <c r="Q12" s="42"/>
+      <c r="R12" s="42"/>
+      <c r="S12" s="42"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="41"/>
+      <c r="V12" s="41"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
-      <c r="J13" s="43"/>
-      <c r="K13" s="43"/>
-      <c r="L13" s="43"/>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="43"/>
-      <c r="P13" s="43"/>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="42"/>
-      <c r="V13" s="42"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="42"/>
+      <c r="L13" s="42"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="41"/>
+      <c r="V13" s="41"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A14" s="42"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="42"/>
-      <c r="V14" s="42"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="41"/>
+      <c r="V14" s="41"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="42"/>
-      <c r="V15" s="42"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="41"/>
+      <c r="V15" s="41"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="42"/>
-      <c r="V16" s="42"/>
+      <c r="A16" s="41"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="42"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="41"/>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="43"/>
-      <c r="T17" s="43"/>
-      <c r="U17" s="42"/>
-      <c r="V17" s="42"/>
+      <c r="A17" s="41"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="42"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="42"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="41"/>
+      <c r="V17" s="41"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="42"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="42"/>
-      <c r="V18" s="42"/>
+      <c r="A18" s="41"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="42"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="41"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="42"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="42"/>
-      <c r="V19" s="42"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="42"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="41"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="42"/>
-      <c r="V20" s="42"/>
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="42"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="42"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="41"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="43"/>
-      <c r="T21" s="43"/>
-      <c r="U21" s="42"/>
-      <c r="V21" s="42"/>
-      <c r="Y21" s="44" t="s">
-        <v>469</v>
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="42"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="42"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="42"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="41"/>
+      <c r="V21" s="41"/>
+      <c r="Y21" s="43" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="42"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="42"/>
-      <c r="V22" s="42"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="42"/>
+      <c r="S22" s="42"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="41"/>
+      <c r="V22" s="41"/>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="42"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="43"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="43"/>
-      <c r="U23" s="42"/>
-      <c r="V23" s="42"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="42"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="42"/>
+      <c r="R23" s="42"/>
+      <c r="S23" s="42"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="41"/>
+      <c r="V23" s="41"/>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="42"/>
-      <c r="V24" s="42"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="42"/>
+      <c r="L24" s="42"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="42"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="42"/>
+      <c r="R24" s="42"/>
+      <c r="S24" s="42"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="41"/>
+      <c r="V24" s="41"/>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="42"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="42"/>
-      <c r="V25" s="42"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="42"/>
+      <c r="L25" s="42"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="42"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="42"/>
+      <c r="T25" s="42"/>
+      <c r="U25" s="41"/>
+      <c r="V25" s="41"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" s="42"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="42"/>
-      <c r="V26" s="42"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="42"/>
+      <c r="L26" s="42"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="42"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="42"/>
+      <c r="S26" s="42"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="41"/>
+      <c r="V26" s="41"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A27" s="42"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="43"/>
-      <c r="U27" s="42"/>
-      <c r="V27" s="42"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="42"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="42"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="42"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="42"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="42"/>
+      <c r="R27" s="42"/>
+      <c r="S27" s="42"/>
+      <c r="T27" s="42"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="42"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="42"/>
-      <c r="V28" s="42"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
+      <c r="E28" s="42"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="42"/>
+      <c r="L28" s="42"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="42"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" s="42"/>
+      <c r="S28" s="42"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="42"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="43"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="43"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="42"/>
-      <c r="V29" s="42"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="42"/>
+      <c r="D29" s="42"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="42"/>
+      <c r="L29" s="42"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="42"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="42"/>
+      <c r="S29" s="42"/>
+      <c r="T29" s="42"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A30" s="42"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="43"/>
-      <c r="R30" s="43"/>
-      <c r="S30" s="43"/>
-      <c r="T30" s="43"/>
-      <c r="U30" s="42"/>
-      <c r="V30" s="42"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
+      <c r="E30" s="42"/>
+      <c r="F30" s="42"/>
+      <c r="G30" s="42"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="42"/>
+      <c r="L30" s="42"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="42"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="42"/>
+      <c r="R30" s="42"/>
+      <c r="S30" s="42"/>
+      <c r="T30" s="42"/>
+      <c r="U30" s="41"/>
+      <c r="V30" s="41"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A31" s="42"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="42"/>
-      <c r="V31" s="42"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="42"/>
+      <c r="L31" s="42"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="42"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="42"/>
+      <c r="Q31" s="42"/>
+      <c r="R31" s="42"/>
+      <c r="S31" s="42"/>
+      <c r="T31" s="42"/>
+      <c r="U31" s="41"/>
+      <c r="V31" s="41"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A32" s="42"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="43"/>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="43"/>
-      <c r="Q32" s="43"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="43"/>
-      <c r="T32" s="43"/>
-      <c r="U32" s="42"/>
-      <c r="V32" s="42"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="42"/>
+      <c r="K32" s="42"/>
+      <c r="L32" s="42"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="42"/>
+      <c r="S32" s="42"/>
+      <c r="T32" s="42"/>
+      <c r="U32" s="41"/>
+      <c r="V32" s="41"/>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A33" s="42"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="43"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="42"/>
-      <c r="V33" s="42"/>
+      <c r="A33" s="41"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="42"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="42"/>
+      <c r="K33" s="42"/>
+      <c r="L33" s="42"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="42"/>
+      <c r="S33" s="42"/>
+      <c r="T33" s="42"/>
+      <c r="U33" s="41"/>
+      <c r="V33" s="41"/>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A34" s="42"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
-      <c r="S34" s="43"/>
-      <c r="T34" s="43"/>
-      <c r="U34" s="42"/>
-      <c r="V34" s="42"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="42"/>
+      <c r="L34" s="42"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="42"/>
+      <c r="S34" s="42"/>
+      <c r="T34" s="42"/>
+      <c r="U34" s="41"/>
+      <c r="V34" s="41"/>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A35" s="42"/>
-      <c r="B35" s="42"/>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-      <c r="E35" s="43"/>
-      <c r="F35" s="43"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="43"/>
-      <c r="P35" s="43"/>
-      <c r="Q35" s="43"/>
-      <c r="R35" s="43"/>
-      <c r="S35" s="43"/>
-      <c r="T35" s="43"/>
-      <c r="U35" s="42"/>
-      <c r="V35" s="42"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="42"/>
+      <c r="D35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="F35" s="42"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="42"/>
+      <c r="I35" s="42"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="42"/>
+      <c r="L35" s="42"/>
+      <c r="M35" s="42"/>
+      <c r="N35" s="42"/>
+      <c r="O35" s="42"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="42"/>
+      <c r="S35" s="42"/>
+      <c r="T35" s="42"/>
+      <c r="U35" s="41"/>
+      <c r="V35" s="41"/>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A36" s="42"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="43"/>
-      <c r="D36" s="43"/>
-      <c r="E36" s="43"/>
-      <c r="F36" s="43"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="43"/>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="43"/>
-      <c r="P36" s="43"/>
-      <c r="Q36" s="43"/>
-      <c r="R36" s="43"/>
-      <c r="S36" s="43"/>
-      <c r="T36" s="43"/>
-      <c r="U36" s="42"/>
-      <c r="V36" s="42"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="42"/>
+      <c r="D36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="F36" s="42"/>
+      <c r="G36" s="42"/>
+      <c r="H36" s="42"/>
+      <c r="I36" s="42"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="42"/>
+      <c r="L36" s="42"/>
+      <c r="M36" s="42"/>
+      <c r="N36" s="42"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="42"/>
+      <c r="R36" s="42"/>
+      <c r="S36" s="42"/>
+      <c r="T36" s="42"/>
+      <c r="U36" s="41"/>
+      <c r="V36" s="41"/>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A37" s="42"/>
-      <c r="B37" s="42"/>
-      <c r="C37" s="43"/>
-      <c r="D37" s="43"/>
-      <c r="E37" s="43"/>
-      <c r="F37" s="43"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="43"/>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
-      <c r="O37" s="43"/>
-      <c r="P37" s="43"/>
-      <c r="Q37" s="43"/>
-      <c r="R37" s="43"/>
-      <c r="S37" s="43"/>
-      <c r="T37" s="43"/>
-      <c r="U37" s="42"/>
-      <c r="V37" s="42"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
+      <c r="H37" s="42"/>
+      <c r="I37" s="42"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="42"/>
+      <c r="L37" s="42"/>
+      <c r="M37" s="42"/>
+      <c r="N37" s="42"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="42"/>
+      <c r="S37" s="42"/>
+      <c r="T37" s="42"/>
+      <c r="U37" s="41"/>
+      <c r="V37" s="41"/>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A38" s="42"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="43"/>
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
-      <c r="O38" s="43"/>
-      <c r="P38" s="43"/>
-      <c r="Q38" s="43"/>
-      <c r="R38" s="43"/>
-      <c r="S38" s="43"/>
-      <c r="T38" s="43"/>
-      <c r="U38" s="42"/>
-      <c r="V38" s="42"/>
+      <c r="A38" s="41"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="42"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="42"/>
+      <c r="N38" s="42"/>
+      <c r="O38" s="42"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="42"/>
+      <c r="S38" s="42"/>
+      <c r="T38" s="42"/>
+      <c r="U38" s="41"/>
+      <c r="V38" s="41"/>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A39" s="42"/>
-      <c r="B39" s="42"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="43"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="43"/>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="K39" s="43"/>
-      <c r="L39" s="43"/>
-      <c r="M39" s="43"/>
-      <c r="N39" s="43"/>
-      <c r="O39" s="43"/>
-      <c r="P39" s="43"/>
-      <c r="Q39" s="43"/>
-      <c r="R39" s="43"/>
-      <c r="S39" s="43"/>
-      <c r="T39" s="43"/>
-      <c r="U39" s="42"/>
-      <c r="V39" s="42"/>
+      <c r="A39" s="41"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="42"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="42"/>
+      <c r="H39" s="42"/>
+      <c r="I39" s="42"/>
+      <c r="J39" s="42"/>
+      <c r="K39" s="42"/>
+      <c r="L39" s="42"/>
+      <c r="M39" s="42"/>
+      <c r="N39" s="42"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="42"/>
+      <c r="R39" s="42"/>
+      <c r="S39" s="42"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="41"/>
+      <c r="V39" s="41"/>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A40" s="42"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="43"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="43"/>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="43"/>
-      <c r="N40" s="43"/>
-      <c r="O40" s="43"/>
-      <c r="P40" s="43"/>
-      <c r="Q40" s="43"/>
-      <c r="R40" s="43"/>
-      <c r="S40" s="43"/>
-      <c r="T40" s="43"/>
-      <c r="U40" s="42"/>
-      <c r="V40" s="42"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="42"/>
+      <c r="D40" s="42"/>
+      <c r="E40" s="42"/>
+      <c r="F40" s="42"/>
+      <c r="G40" s="42"/>
+      <c r="H40" s="42"/>
+      <c r="I40" s="42"/>
+      <c r="J40" s="42"/>
+      <c r="K40" s="42"/>
+      <c r="L40" s="42"/>
+      <c r="M40" s="42"/>
+      <c r="N40" s="42"/>
+      <c r="O40" s="42"/>
+      <c r="P40" s="42"/>
+      <c r="Q40" s="42"/>
+      <c r="R40" s="42"/>
+      <c r="S40" s="42"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="41"/>
+      <c r="V40" s="41"/>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A41" s="42"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="43"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="43"/>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="43"/>
-      <c r="N41" s="43"/>
-      <c r="O41" s="43"/>
-      <c r="P41" s="43"/>
-      <c r="Q41" s="43"/>
-      <c r="R41" s="43"/>
-      <c r="S41" s="43"/>
-      <c r="T41" s="43"/>
-      <c r="U41" s="42"/>
-      <c r="V41" s="42"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="42"/>
+      <c r="N41" s="42"/>
+      <c r="O41" s="42"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="42"/>
+      <c r="T41" s="42"/>
+      <c r="U41" s="41"/>
+      <c r="V41" s="41"/>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A42" s="42"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="43"/>
-      <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="43"/>
-      <c r="P42" s="43"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="43"/>
-      <c r="S42" s="43"/>
-      <c r="T42" s="43"/>
-      <c r="U42" s="42"/>
-      <c r="V42" s="42"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="42"/>
+      <c r="D42" s="42"/>
+      <c r="E42" s="42"/>
+      <c r="F42" s="42"/>
+      <c r="G42" s="42"/>
+      <c r="H42" s="42"/>
+      <c r="I42" s="42"/>
+      <c r="J42" s="42"/>
+      <c r="K42" s="42"/>
+      <c r="L42" s="42"/>
+      <c r="M42" s="42"/>
+      <c r="N42" s="42"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="42"/>
+      <c r="S42" s="42"/>
+      <c r="T42" s="42"/>
+      <c r="U42" s="41"/>
+      <c r="V42" s="41"/>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A43" s="42"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="43"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="43"/>
-      <c r="H43" s="43"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="43"/>
-      <c r="L43" s="43"/>
-      <c r="M43" s="43"/>
-      <c r="N43" s="43"/>
-      <c r="O43" s="43"/>
-      <c r="P43" s="43"/>
-      <c r="Q43" s="43"/>
-      <c r="R43" s="43"/>
-      <c r="S43" s="43"/>
-      <c r="T43" s="43"/>
-      <c r="U43" s="42"/>
-      <c r="V43" s="42"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="42"/>
+      <c r="D43" s="42"/>
+      <c r="E43" s="42"/>
+      <c r="F43" s="42"/>
+      <c r="G43" s="42"/>
+      <c r="H43" s="42"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+      <c r="K43" s="42"/>
+      <c r="L43" s="42"/>
+      <c r="M43" s="42"/>
+      <c r="N43" s="42"/>
+      <c r="O43" s="42"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="42"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="41"/>
+      <c r="V43" s="41"/>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A44" s="42"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
-      <c r="L44" s="43"/>
-      <c r="M44" s="43"/>
-      <c r="N44" s="43"/>
-      <c r="O44" s="43"/>
-      <c r="P44" s="43"/>
-      <c r="Q44" s="43"/>
-      <c r="R44" s="43"/>
-      <c r="S44" s="43"/>
-      <c r="T44" s="43"/>
-      <c r="U44" s="42"/>
-      <c r="V44" s="42"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="42"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="42"/>
+      <c r="H44" s="42"/>
+      <c r="I44" s="42"/>
+      <c r="J44" s="42"/>
+      <c r="K44" s="42"/>
+      <c r="L44" s="42"/>
+      <c r="M44" s="42"/>
+      <c r="N44" s="42"/>
+      <c r="O44" s="42"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="42"/>
+      <c r="S44" s="42"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="41"/>
+      <c r="V44" s="41"/>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A45" s="42"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-      <c r="N45" s="43"/>
-      <c r="O45" s="43"/>
-      <c r="P45" s="43"/>
-      <c r="Q45" s="43"/>
-      <c r="R45" s="43"/>
-      <c r="S45" s="43"/>
-      <c r="T45" s="43"/>
-      <c r="U45" s="42"/>
-      <c r="V45" s="42"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="42"/>
+      <c r="D45" s="42"/>
+      <c r="E45" s="42"/>
+      <c r="F45" s="42"/>
+      <c r="G45" s="42"/>
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42"/>
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="M45" s="42"/>
+      <c r="N45" s="42"/>
+      <c r="O45" s="42"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="42"/>
+      <c r="S45" s="42"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="41"/>
+      <c r="V45" s="41"/>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A46" s="42"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="43"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="43"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="43"/>
-      <c r="L46" s="43"/>
-      <c r="M46" s="43"/>
-      <c r="N46" s="43"/>
-      <c r="O46" s="43"/>
-      <c r="P46" s="43"/>
-      <c r="Q46" s="43"/>
-      <c r="R46" s="43"/>
-      <c r="S46" s="43"/>
-      <c r="T46" s="43"/>
-      <c r="U46" s="42"/>
-      <c r="V46" s="42"/>
+      <c r="A46" s="41"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="42"/>
+      <c r="D46" s="42"/>
+      <c r="E46" s="42"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42"/>
+      <c r="K46" s="42"/>
+      <c r="L46" s="42"/>
+      <c r="M46" s="42"/>
+      <c r="N46" s="42"/>
+      <c r="O46" s="42"/>
+      <c r="P46" s="42"/>
+      <c r="Q46" s="42"/>
+      <c r="R46" s="42"/>
+      <c r="S46" s="42"/>
+      <c r="T46" s="42"/>
+      <c r="U46" s="41"/>
+      <c r="V46" s="41"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A47" s="42"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="43"/>
-      <c r="I47" s="43"/>
-      <c r="J47" s="43"/>
-      <c r="K47" s="43"/>
-      <c r="L47" s="43"/>
-      <c r="M47" s="43"/>
-      <c r="N47" s="43"/>
-      <c r="O47" s="43"/>
-      <c r="P47" s="43"/>
-      <c r="Q47" s="43"/>
-      <c r="R47" s="43"/>
-      <c r="S47" s="43"/>
-      <c r="T47" s="43"/>
-      <c r="U47" s="42"/>
-      <c r="V47" s="42"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="42"/>
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42"/>
+      <c r="K47" s="42"/>
+      <c r="L47" s="42"/>
+      <c r="M47" s="42"/>
+      <c r="N47" s="42"/>
+      <c r="O47" s="42"/>
+      <c r="P47" s="42"/>
+      <c r="Q47" s="42"/>
+      <c r="R47" s="42"/>
+      <c r="S47" s="42"/>
+      <c r="T47" s="42"/>
+      <c r="U47" s="41"/>
+      <c r="V47" s="41"/>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A48" s="42"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="43"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="43"/>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-      <c r="J48" s="43"/>
-      <c r="K48" s="43"/>
-      <c r="L48" s="43"/>
-      <c r="M48" s="43"/>
-      <c r="N48" s="43"/>
-      <c r="O48" s="43"/>
-      <c r="P48" s="43"/>
-      <c r="Q48" s="43"/>
-      <c r="R48" s="43"/>
-      <c r="S48" s="43"/>
-      <c r="T48" s="43"/>
-      <c r="U48" s="42"/>
-      <c r="V48" s="42"/>
+      <c r="A48" s="41"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="42"/>
+      <c r="D48" s="42"/>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42"/>
+      <c r="K48" s="42"/>
+      <c r="L48" s="42"/>
+      <c r="M48" s="42"/>
+      <c r="N48" s="42"/>
+      <c r="O48" s="42"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="42"/>
+      <c r="R48" s="42"/>
+      <c r="S48" s="42"/>
+      <c r="T48" s="42"/>
+      <c r="U48" s="41"/>
+      <c r="V48" s="41"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A49" s="42"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="43"/>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="43"/>
-      <c r="M49" s="43"/>
-      <c r="N49" s="43"/>
-      <c r="O49" s="43"/>
-      <c r="P49" s="43"/>
-      <c r="Q49" s="43"/>
-      <c r="R49" s="43"/>
-      <c r="S49" s="43"/>
-      <c r="T49" s="43"/>
-      <c r="U49" s="42"/>
-      <c r="V49" s="42"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="42"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42"/>
+      <c r="K49" s="42"/>
+      <c r="L49" s="42"/>
+      <c r="M49" s="42"/>
+      <c r="N49" s="42"/>
+      <c r="O49" s="42"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="42"/>
+      <c r="R49" s="42"/>
+      <c r="S49" s="42"/>
+      <c r="T49" s="42"/>
+      <c r="U49" s="41"/>
+      <c r="V49" s="41"/>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A50" s="42"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="43"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="43"/>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="43"/>
-      <c r="L50" s="43"/>
-      <c r="M50" s="43"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="43"/>
-      <c r="P50" s="43"/>
-      <c r="Q50" s="43"/>
-      <c r="R50" s="43"/>
-      <c r="S50" s="43"/>
-      <c r="T50" s="43"/>
-      <c r="U50" s="42"/>
-      <c r="V50" s="42"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="42"/>
+      <c r="D50" s="42"/>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+      <c r="I50" s="42"/>
+      <c r="J50" s="42"/>
+      <c r="K50" s="42"/>
+      <c r="L50" s="42"/>
+      <c r="M50" s="42"/>
+      <c r="N50" s="42"/>
+      <c r="O50" s="42"/>
+      <c r="P50" s="42"/>
+      <c r="Q50" s="42"/>
+      <c r="R50" s="42"/>
+      <c r="S50" s="42"/>
+      <c r="T50" s="42"/>
+      <c r="U50" s="41"/>
+      <c r="V50" s="41"/>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A51" s="42"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="43"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="43"/>
-      <c r="I51" s="43"/>
-      <c r="J51" s="43"/>
-      <c r="K51" s="43"/>
-      <c r="L51" s="43"/>
-      <c r="M51" s="43"/>
-      <c r="N51" s="43"/>
-      <c r="O51" s="43"/>
-      <c r="P51" s="43"/>
-      <c r="Q51" s="43"/>
-      <c r="R51" s="43"/>
-      <c r="S51" s="43"/>
-      <c r="T51" s="43"/>
-      <c r="U51" s="42"/>
-      <c r="V51" s="42"/>
+      <c r="A51" s="41"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
+      <c r="K51" s="42"/>
+      <c r="L51" s="42"/>
+      <c r="M51" s="42"/>
+      <c r="N51" s="42"/>
+      <c r="O51" s="42"/>
+      <c r="P51" s="42"/>
+      <c r="Q51" s="42"/>
+      <c r="R51" s="42"/>
+      <c r="S51" s="42"/>
+      <c r="T51" s="42"/>
+      <c r="U51" s="41"/>
+      <c r="V51" s="41"/>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A52" s="42"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="43"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="43"/>
-      <c r="H52" s="43"/>
-      <c r="I52" s="43"/>
-      <c r="J52" s="43"/>
-      <c r="K52" s="43"/>
-      <c r="L52" s="43"/>
-      <c r="M52" s="43"/>
-      <c r="N52" s="43"/>
-      <c r="O52" s="43"/>
-      <c r="P52" s="43"/>
-      <c r="Q52" s="43"/>
-      <c r="R52" s="43"/>
-      <c r="S52" s="43"/>
-      <c r="T52" s="43"/>
-      <c r="U52" s="42"/>
-      <c r="V52" s="42"/>
+      <c r="A52" s="41"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="42"/>
+      <c r="D52" s="42"/>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+      <c r="I52" s="42"/>
+      <c r="J52" s="42"/>
+      <c r="K52" s="42"/>
+      <c r="L52" s="42"/>
+      <c r="M52" s="42"/>
+      <c r="N52" s="42"/>
+      <c r="O52" s="42"/>
+      <c r="P52" s="42"/>
+      <c r="Q52" s="42"/>
+      <c r="R52" s="42"/>
+      <c r="S52" s="42"/>
+      <c r="T52" s="42"/>
+      <c r="U52" s="41"/>
+      <c r="V52" s="41"/>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A53" s="42"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="43"/>
-      <c r="D53" s="43"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="43"/>
-      <c r="H53" s="43"/>
-      <c r="I53" s="43"/>
-      <c r="J53" s="43"/>
-      <c r="K53" s="43"/>
-      <c r="L53" s="43"/>
-      <c r="M53" s="43"/>
-      <c r="N53" s="43"/>
-      <c r="O53" s="43"/>
-      <c r="P53" s="43"/>
-      <c r="Q53" s="43"/>
-      <c r="R53" s="43"/>
-      <c r="S53" s="43"/>
-      <c r="T53" s="43"/>
-      <c r="U53" s="42"/>
-      <c r="V53" s="42"/>
+      <c r="A53" s="41"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="42"/>
+      <c r="D53" s="42"/>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+      <c r="I53" s="42"/>
+      <c r="J53" s="42"/>
+      <c r="K53" s="42"/>
+      <c r="L53" s="42"/>
+      <c r="M53" s="42"/>
+      <c r="N53" s="42"/>
+      <c r="O53" s="42"/>
+      <c r="P53" s="42"/>
+      <c r="Q53" s="42"/>
+      <c r="R53" s="42"/>
+      <c r="S53" s="42"/>
+      <c r="T53" s="42"/>
+      <c r="U53" s="41"/>
+      <c r="V53" s="41"/>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A54" s="42"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="43"/>
-      <c r="H54" s="43"/>
-      <c r="I54" s="43"/>
-      <c r="J54" s="43"/>
-      <c r="K54" s="43"/>
-      <c r="L54" s="43"/>
-      <c r="M54" s="43"/>
-      <c r="N54" s="43"/>
-      <c r="O54" s="43"/>
-      <c r="P54" s="43"/>
-      <c r="Q54" s="43"/>
-      <c r="R54" s="43"/>
-      <c r="S54" s="43"/>
-      <c r="T54" s="43"/>
-      <c r="U54" s="42"/>
-      <c r="V54" s="42"/>
+      <c r="A54" s="41"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="42"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+      <c r="I54" s="42"/>
+      <c r="J54" s="42"/>
+      <c r="K54" s="42"/>
+      <c r="L54" s="42"/>
+      <c r="M54" s="42"/>
+      <c r="N54" s="42"/>
+      <c r="O54" s="42"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="42"/>
+      <c r="R54" s="42"/>
+      <c r="S54" s="42"/>
+      <c r="T54" s="42"/>
+      <c r="U54" s="41"/>
+      <c r="V54" s="41"/>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A55" s="42"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="43"/>
-      <c r="D55" s="43"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="43"/>
-      <c r="H55" s="43"/>
-      <c r="I55" s="43"/>
-      <c r="J55" s="43"/>
-      <c r="K55" s="43"/>
-      <c r="L55" s="43"/>
-      <c r="M55" s="43"/>
-      <c r="N55" s="43"/>
-      <c r="O55" s="43"/>
-      <c r="P55" s="43"/>
-      <c r="Q55" s="43"/>
-      <c r="R55" s="43"/>
-      <c r="S55" s="43"/>
-      <c r="T55" s="43"/>
-      <c r="U55" s="42"/>
-      <c r="V55" s="42"/>
+      <c r="A55" s="41"/>
+      <c r="B55" s="41"/>
+      <c r="C55" s="42"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+      <c r="I55" s="42"/>
+      <c r="J55" s="42"/>
+      <c r="K55" s="42"/>
+      <c r="L55" s="42"/>
+      <c r="M55" s="42"/>
+      <c r="N55" s="42"/>
+      <c r="O55" s="42"/>
+      <c r="P55" s="42"/>
+      <c r="Q55" s="42"/>
+      <c r="R55" s="42"/>
+      <c r="S55" s="42"/>
+      <c r="T55" s="42"/>
+      <c r="U55" s="41"/>
+      <c r="V55" s="41"/>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.35">
-      <c r="A56" s="42"/>
-      <c r="B56" s="42"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="42"/>
-      <c r="F56" s="42"/>
-      <c r="G56" s="42"/>
-      <c r="H56" s="42"/>
-      <c r="I56" s="42"/>
-      <c r="J56" s="42"/>
-      <c r="K56" s="42"/>
-      <c r="L56" s="42"/>
-      <c r="M56" s="42"/>
-      <c r="N56" s="42"/>
-      <c r="O56" s="42"/>
-      <c r="P56" s="42"/>
-      <c r="Q56" s="42"/>
-      <c r="R56" s="42"/>
-      <c r="S56" s="42"/>
-      <c r="T56" s="42"/>
-      <c r="U56" s="42"/>
-      <c r="V56" s="42"/>
+      <c r="A56" s="41"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41"/>
+      <c r="J56" s="41"/>
+      <c r="K56" s="41"/>
+      <c r="L56" s="41"/>
+      <c r="M56" s="41"/>
+      <c r="N56" s="41"/>
+      <c r="O56" s="41"/>
+      <c r="P56" s="41"/>
+      <c r="Q56" s="41"/>
+      <c r="R56" s="41"/>
+      <c r="S56" s="41"/>
+      <c r="T56" s="41"/>
+      <c r="U56" s="41"/>
+      <c r="V56" s="41"/>
     </row>
     <row r="57" spans="1:22" ht="20.5" x14ac:dyDescent="0.45">
-      <c r="A57" s="73"/>
-      <c r="B57" s="73"/>
-      <c r="C57" s="73"/>
-      <c r="D57" s="73"/>
-      <c r="E57" s="42"/>
-      <c r="F57" s="42"/>
-      <c r="G57" s="42"/>
-      <c r="H57" s="42"/>
-      <c r="I57" s="42"/>
-      <c r="J57" s="42"/>
-      <c r="K57" s="42"/>
-      <c r="L57" s="42"/>
-      <c r="M57" s="42"/>
-      <c r="N57" s="42"/>
-      <c r="O57" s="42"/>
-      <c r="P57" s="42"/>
-      <c r="Q57" s="73"/>
-      <c r="R57" s="73"/>
-      <c r="S57" s="73"/>
-      <c r="T57" s="73"/>
-      <c r="U57" s="73"/>
-      <c r="V57" s="42"/>
+      <c r="A57" s="56"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="41"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
+      <c r="H57" s="41"/>
+      <c r="I57" s="41"/>
+      <c r="J57" s="41"/>
+      <c r="K57" s="41"/>
+      <c r="L57" s="41"/>
+      <c r="M57" s="41"/>
+      <c r="N57" s="41"/>
+      <c r="O57" s="41"/>
+      <c r="P57" s="41"/>
+      <c r="Q57" s="56"/>
+      <c r="R57" s="56"/>
+      <c r="S57" s="56"/>
+      <c r="T57" s="56"/>
+      <c r="U57" s="56"/>
+      <c r="V57" s="41"/>
     </row>
     <row r="58" spans="1:22" ht="20.5" x14ac:dyDescent="0.45">
-      <c r="A58" s="73"/>
-      <c r="B58" s="73"/>
-      <c r="C58" s="73"/>
-      <c r="D58" s="73"/>
-      <c r="E58" s="42"/>
-      <c r="F58" s="42"/>
-      <c r="G58" s="42"/>
-      <c r="H58" s="42"/>
-      <c r="I58" s="42"/>
-      <c r="J58" s="42"/>
-      <c r="K58" s="42"/>
-      <c r="L58" s="42"/>
-      <c r="M58" s="42"/>
-      <c r="N58" s="42"/>
-      <c r="O58" s="42"/>
-      <c r="P58" s="42"/>
-      <c r="Q58" s="73"/>
-      <c r="R58" s="73"/>
-      <c r="S58" s="73"/>
-      <c r="T58" s="73"/>
-      <c r="U58" s="73"/>
-      <c r="V58" s="42"/>
+      <c r="A58" s="56"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="41"/>
+      <c r="J58" s="41"/>
+      <c r="K58" s="41"/>
+      <c r="L58" s="41"/>
+      <c r="M58" s="41"/>
+      <c r="N58" s="41"/>
+      <c r="O58" s="41"/>
+      <c r="P58" s="41"/>
+      <c r="Q58" s="56"/>
+      <c r="R58" s="56"/>
+      <c r="S58" s="56"/>
+      <c r="T58" s="56"/>
+      <c r="U58" s="56"/>
+      <c r="V58" s="41"/>
     </row>
     <row r="59" spans="1:22" ht="20.5" x14ac:dyDescent="0.45">
-      <c r="A59" s="42"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="42"/>
-      <c r="D59" s="42"/>
-      <c r="E59" s="42"/>
-      <c r="F59" s="42"/>
-      <c r="G59" s="42"/>
-      <c r="H59" s="42"/>
-      <c r="I59" s="42"/>
-      <c r="J59" s="42"/>
-      <c r="K59" s="42"/>
-      <c r="L59" s="42"/>
-      <c r="M59" s="42"/>
-      <c r="N59" s="42"/>
-      <c r="O59" s="42"/>
-      <c r="P59" s="42"/>
-      <c r="Q59" s="42"/>
-      <c r="R59" s="46"/>
-      <c r="S59" s="46"/>
-      <c r="T59" s="46"/>
-      <c r="U59" s="46"/>
-      <c r="V59" s="42"/>
+      <c r="A59" s="41"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="41"/>
+      <c r="E59" s="41"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="41"/>
+      <c r="H59" s="41"/>
+      <c r="I59" s="41"/>
+      <c r="J59" s="41"/>
+      <c r="K59" s="41"/>
+      <c r="L59" s="41"/>
+      <c r="M59" s="41"/>
+      <c r="N59" s="41"/>
+      <c r="O59" s="41"/>
+      <c r="P59" s="41"/>
+      <c r="Q59" s="41"/>
+      <c r="R59" s="45"/>
+      <c r="S59" s="45"/>
+      <c r="T59" s="45"/>
+      <c r="U59" s="45"/>
+      <c r="V59" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -21509,16 +18285,17 @@
     <mergeCell ref="Q58:U58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId2"/>
+        <x14:slicer r:id="rId3"/>
       </x14:slicerList>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{7E03D99C-DC04-49d9-9315-930204A7B6E9}">
       <x15:timelineRefs>
-        <x15:timelineRef r:id="rId3"/>
+        <x15:timelineRef r:id="rId4"/>
       </x15:timelineRefs>
     </ext>
   </extLst>
@@ -44575,7 +41352,7 @@
   <sheetData>
     <row r="1" spans="1:27" ht="20" x14ac:dyDescent="0.4">
       <c r="A1" s="58" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="B1" s="58"/>
       <c r="C1" s="58"/>
@@ -44589,13 +41366,13 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A5" s="59" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="B5" s="59"/>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="60" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="B6" s="60"/>
       <c r="C6" s="60"/>
@@ -44629,7 +41406,7 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="61" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B9" s="61"/>
     </row>
@@ -44639,30 +41416,30 @@
       </c>
       <c r="B10" s="14">
         <f>Dashboard!Y7</f>
-        <v>0</v>
+        <v>47228.340000000004</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="B11" s="14" t="str">
         <f>Dashboard!Z7</f>
-        <v>North</v>
+        <v>South</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="B12" s="14" t="str">
         <f>Dashboard!AA7</f>
-        <v>Appliances</v>
+        <v>Electronics</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="B13" s="14" t="str">
         <f>Dashboard!AB7</f>
@@ -44671,18 +41448,18 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
-        <v>480</v>
-      </c>
-      <c r="B14" s="55">
+        <v>476</v>
+      </c>
+      <c r="B14" s="54">
         <f>COUNTA(Dataset!A:A)-1</f>
         <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A15" s="56" t="s">
-        <v>481</v>
-      </c>
-      <c r="B15" s="55">
+      <c r="A15" s="55" t="s">
+        <v>477</v>
+      </c>
+      <c r="B15" s="54">
         <f>SUM(Dataset!H:H)</f>
         <v>753</v>
       </c>
@@ -44700,12 +41477,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9876C804-486F-4956-B556-74D67F70E355}">
-  <dimension ref="A3:F21"/>
+  <dimension ref="A3:F19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -44725,30 +41502,74 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B4" s="39">
-        <v>1119.8399999999999</v>
+        <v>13489.69</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F4" s="39">
-        <v>1119.8399999999999</v>
+        <v>34589.120000000003</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="39">
+        <v>13329.499999999998</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="39">
+        <v>10699.499999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="39">
+        <v>10309.64</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="39">
+        <v>1939.72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="39">
+        <v>8749.6200000000008</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="B5" s="39">
-        <v>1119.8399999999999</v>
-      </c>
-      <c r="E5" s="13" t="s">
+      <c r="F7" s="39">
+        <v>47228.34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="39">
+        <v>1349.89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="13" t="s">
         <v>460</v>
       </c>
-      <c r="F5" s="39">
-        <v>1119.8399999999999</v>
+      <c r="B9" s="39">
+        <v>47228.340000000004</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -44758,92 +41579,46 @@
       <c r="B15" s="13" t="s">
         <v>461</v>
       </c>
-      <c r="E15" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>461</v>
-      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>27</v>
       </c>
       <c r="B16" s="39">
-        <v>179.97</v>
-      </c>
-      <c r="E16" s="72" t="s">
-        <v>462</v>
-      </c>
-      <c r="F16" s="71">
-        <v>879.86999999999989</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>15459.349999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="13" t="s">
         <v>36</v>
       </c>
       <c r="B17" s="39">
-        <v>379.94</v>
-      </c>
-      <c r="E17" s="41" t="s">
-        <v>464</v>
-      </c>
-      <c r="F17" s="39">
-        <v>439.92999999999995</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>15609.599999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
         <v>22</v>
       </c>
       <c r="B18" s="39">
-        <v>559.92999999999995</v>
-      </c>
-      <c r="E18" s="41" t="s">
-        <v>465</v>
-      </c>
-      <c r="F18" s="39">
-        <v>439.94</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>16159.39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
         <v>460</v>
       </c>
       <c r="B19" s="39">
-        <v>1119.8399999999999</v>
-      </c>
-      <c r="E19" s="72" t="s">
-        <v>463</v>
-      </c>
-      <c r="F19" s="71">
-        <v>239.97</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E20" s="41" t="s">
-        <v>464</v>
-      </c>
-      <c r="F20" s="39">
-        <v>239.97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="E21" s="13" t="s">
-        <v>460</v>
-      </c>
-      <c r="F21" s="39">
-        <v>1119.8399999999999</v>
+        <v>47228.34</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId6"/>
+        <x14:slicer r:id="rId5"/>
       </x14:slicerList>
     </ext>
   </extLst>
@@ -46172,7 +42947,7 @@
       </c>
       <c r="N25" s="5">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O25" s="5">
         <f>EOMONTH(Dataset!B25,0)</f>
@@ -50384,7 +47159,7 @@
       </c>
       <c r="N106" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O106" s="5">
         <f>EOMONTH(Dataset!B106,0)</f>
@@ -58716,82 +55491,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="46" t="s">
         <v>404</v>
       </c>
-      <c r="D1" s="48" t="s">
-        <v>470</v>
-      </c>
-      <c r="G1" s="54" t="s">
-        <v>471</v>
+      <c r="D1" s="47" t="s">
+        <v>466</v>
+      </c>
+      <c r="G1" s="53" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="49" t="str" cm="1">
+      <c r="A2" s="48" t="str" cm="1">
         <f t="array" ref="A2:A42">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Dataset!D:D,Dataset!L:L="Premium"))</f>
         <v>Joseph Jackson</v>
       </c>
-      <c r="D2" s="51" t="str" cm="1">
+      <c r="D2" s="50" t="str" cm="1">
         <f t="array" ref="D2:D32">_xlfn.UNIQUE(_xlfn._xlws.FILTER(Dataset!D:D,Dataset!K:K="North"))</f>
         <v>Kathleen Bennett</v>
       </c>
-      <c r="G2" s="53" t="str" cm="1">
+      <c r="G2" s="52" t="str" cm="1">
         <f t="array" ref="G2:G27">_xlfn._xlws.FILTER(_xlfn.ANCHORARRAY(A2),COUNTIF(_xlfn.ANCHORARRAY(D2),_xlfn.ANCHORARRAY(A2))&gt;0)</f>
         <v>Kathleen Bennett</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="49" t="str">
+      <c r="A3" s="48" t="str">
         <v>Kathleen Bennett</v>
       </c>
-      <c r="D3" s="51" t="str">
+      <c r="D3" s="50" t="str">
         <v>Michael Brown</v>
       </c>
-      <c r="G3" s="53" t="str">
+      <c r="G3" s="52" t="str">
         <v>Michael Brown</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="49" t="str">
+      <c r="A4" s="48" t="str">
         <v>Michael Brown</v>
       </c>
-      <c r="D4" s="51" t="str">
+      <c r="D4" s="50" t="str">
         <v>Peter Richardson</v>
       </c>
-      <c r="G4" s="53" t="str">
+      <c r="G4" s="52" t="str">
         <v>Karen Hill</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="49" t="str">
+      <c r="A5" s="48" t="str">
         <v>Karen Hill</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="50" t="str">
         <v>Dennis Gray</v>
       </c>
-      <c r="G5" s="53" t="str">
+      <c r="G5" s="52" t="str">
         <v>Peter Richardson</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="49" t="str">
+      <c r="A6" s="48" t="str">
         <v>Peter Richardson</v>
       </c>
-      <c r="D6" s="51" t="str">
+      <c r="D6" s="50" t="str">
         <v>George Adams</v>
       </c>
-      <c r="G6" s="53" t="str">
+      <c r="G6" s="52" t="str">
         <v>Mark Carter</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="50" t="str">
+      <c r="A7" s="49" t="str">
         <v>Mark Carter</v>
       </c>
-      <c r="D7" s="52" t="str">
+      <c r="D7" s="51" t="str">
         <v>Mark Carter</v>
       </c>
-      <c r="G7" s="53" t="str">
+      <c r="G7" s="52" t="str">
         <v>Virginia Sanders</v>
       </c>
     </row>
@@ -58799,10 +55574,10 @@
       <c r="A8" s="14" t="str">
         <v>Virginia Sanders</v>
       </c>
-      <c r="D8" s="52" t="str">
+      <c r="D8" s="51" t="str">
         <v>Maria Garcia</v>
       </c>
-      <c r="G8" s="53" t="str">
+      <c r="G8" s="52" t="str">
         <v>Patricia Moore</v>
       </c>
     </row>
@@ -58810,10 +55585,10 @@
       <c r="A9" s="14" t="str">
         <v>Linda Martin</v>
       </c>
-      <c r="D9" s="52" t="str">
+      <c r="D9" s="51" t="str">
         <v>Virginia Sanders</v>
       </c>
-      <c r="G9" s="53" t="str">
+      <c r="G9" s="52" t="str">
         <v>Steven Turner</v>
       </c>
     </row>
@@ -58821,10 +55596,10 @@
       <c r="A10" s="14" t="str">
         <v>Patricia Moore</v>
       </c>
-      <c r="D10" s="52" t="str">
+      <c r="D10" s="51" t="str">
         <v>Cynthia Price</v>
       </c>
-      <c r="G10" s="53" t="str">
+      <c r="G10" s="52" t="str">
         <v>Harry Morgan</v>
       </c>
     </row>
@@ -58832,10 +55607,10 @@
       <c r="A11" s="14" t="str">
         <v>Emma Wilson</v>
       </c>
-      <c r="D11" s="52" t="str">
+      <c r="D11" s="51" t="str">
         <v>Patricia Moore</v>
       </c>
-      <c r="G11" s="53" t="str">
+      <c r="G11" s="52" t="str">
         <v>Betty Campbell</v>
       </c>
     </row>
@@ -58843,10 +55618,10 @@
       <c r="A12" s="14" t="str">
         <v>Kevin Scott</v>
       </c>
-      <c r="D12" s="52" t="str">
+      <c r="D12" s="51" t="str">
         <v>Steven Turner</v>
       </c>
-      <c r="G12" s="53" t="str">
+      <c r="G12" s="52" t="str">
         <v>Barbara Young</v>
       </c>
     </row>
@@ -58854,10 +55629,10 @@
       <c r="A13" s="14" t="str">
         <v>Steven Turner</v>
       </c>
-      <c r="D13" s="52" t="str">
+      <c r="D13" s="51" t="str">
         <v>Daniel King</v>
       </c>
-      <c r="G13" s="53" t="str">
+      <c r="G13" s="52" t="str">
         <v>Frank Torres</v>
       </c>
     </row>
@@ -58865,10 +55640,10 @@
       <c r="A14" s="14" t="str">
         <v>Harry Morgan</v>
       </c>
-      <c r="D14" s="52" t="str">
+      <c r="D14" s="51" t="str">
         <v>Charles Allen</v>
       </c>
-      <c r="G14" s="53" t="str">
+      <c r="G14" s="52" t="str">
         <v>David Martinez</v>
       </c>
     </row>
@@ -58876,10 +55651,10 @@
       <c r="A15" s="14" t="str">
         <v>Lisa Anderson</v>
       </c>
-      <c r="D15" s="52" t="str">
+      <c r="D15" s="51" t="str">
         <v>Margaret Wright</v>
       </c>
-      <c r="G15" s="53" t="str">
+      <c r="G15" s="52" t="str">
         <v>Margaret Wright</v>
       </c>
     </row>
@@ -58887,10 +55662,10 @@
       <c r="A16" s="14" t="str">
         <v>Edward Mitchell</v>
       </c>
-      <c r="D16" s="52" t="str">
+      <c r="D16" s="51" t="str">
         <v>Barbara Young</v>
       </c>
-      <c r="G16" s="53" t="str">
+      <c r="G16" s="52" t="str">
         <v>Sandra Phillips</v>
       </c>
     </row>
@@ -58898,10 +55673,10 @@
       <c r="A17" s="14" t="str">
         <v>Betty Campbell</v>
       </c>
-      <c r="D17" s="52" t="str">
+      <c r="D17" s="51" t="str">
         <v>Frank Torres</v>
       </c>
-      <c r="G17" s="53" t="str">
+      <c r="G17" s="52" t="str">
         <v>Paul Baker</v>
       </c>
     </row>
@@ -58909,10 +55684,10 @@
       <c r="A18" s="14" t="str">
         <v>Barbara Young</v>
       </c>
-      <c r="D18" s="52" t="str">
+      <c r="D18" s="51" t="str">
         <v>Karen Hill</v>
       </c>
-      <c r="G18" s="53" t="str">
+      <c r="G18" s="52" t="str">
         <v>Dorothy Nelson</v>
       </c>
     </row>
@@ -58920,10 +55695,10 @@
       <c r="A19" s="14" t="str">
         <v>Frank Torres</v>
       </c>
-      <c r="D19" s="52" t="str">
+      <c r="D19" s="51" t="str">
         <v>David Martinez</v>
       </c>
-      <c r="G19" s="53" t="str">
+      <c r="G19" s="52" t="str">
         <v>Daniel King</v>
       </c>
     </row>
@@ -58931,10 +55706,10 @@
       <c r="A20" s="14" t="str">
         <v>David Martinez</v>
       </c>
-      <c r="D20" s="52" t="str">
+      <c r="D20" s="51" t="str">
         <v>Betty Campbell</v>
       </c>
-      <c r="G20" s="53" t="str">
+      <c r="G20" s="52" t="str">
         <v>Maria Garcia</v>
       </c>
     </row>
@@ -58942,10 +55717,10 @@
       <c r="A21" s="14" t="str">
         <v>Margaret Wright</v>
       </c>
-      <c r="D21" s="52" t="str">
+      <c r="D21" s="51" t="str">
         <v>Sandra Phillips</v>
       </c>
-      <c r="G21" s="53" t="str">
+      <c r="G21" s="52" t="str">
         <v>Charles Allen</v>
       </c>
     </row>
@@ -58953,10 +55728,10 @@
       <c r="A22" s="14" t="str">
         <v>Lawrence Reed</v>
       </c>
-      <c r="D22" s="52" t="str">
+      <c r="D22" s="51" t="str">
         <v>Paul Baker</v>
       </c>
-      <c r="G22" s="53" t="str">
+      <c r="G22" s="52" t="str">
         <v>Michelle Rogers</v>
       </c>
     </row>
@@ -58964,10 +55739,10 @@
       <c r="A23" s="14" t="str">
         <v>Gerald Murphy</v>
       </c>
-      <c r="D23" s="52" t="str">
+      <c r="D23" s="51" t="str">
         <v>Jennifer Taylor</v>
       </c>
-      <c r="G23" s="53" t="str">
+      <c r="G23" s="52" t="str">
         <v>Douglas Watson</v>
       </c>
     </row>
@@ -58975,10 +55750,10 @@
       <c r="A24" s="14" t="str">
         <v>Carol Evans</v>
       </c>
-      <c r="D24" s="52" t="str">
+      <c r="D24" s="51" t="str">
         <v>Ruth Brooks</v>
       </c>
-      <c r="G24" s="53" t="str">
+      <c r="G24" s="52" t="str">
         <v>Ruth Brooks</v>
       </c>
     </row>
@@ -58986,10 +55761,10 @@
       <c r="A25" s="14" t="str">
         <v>Sandra Phillips</v>
       </c>
-      <c r="D25" s="52" t="str">
+      <c r="D25" s="51" t="str">
         <v>Raymond Ross</v>
       </c>
-      <c r="G25" s="53" t="str">
+      <c r="G25" s="52" t="str">
         <v>Arthur Edwards</v>
       </c>
     </row>
@@ -58997,10 +55772,10 @@
       <c r="A26" s="14" t="str">
         <v>Paul Baker</v>
       </c>
-      <c r="D26" s="52" t="str">
+      <c r="D26" s="51" t="str">
         <v>Douglas Watson</v>
       </c>
-      <c r="G26" s="53" t="str">
+      <c r="G26" s="52" t="str">
         <v>Dennis Gray</v>
       </c>
     </row>
@@ -59008,10 +55783,10 @@
       <c r="A27" s="14" t="str">
         <v>Dorothy Nelson</v>
       </c>
-      <c r="D27" s="52" t="str">
+      <c r="D27" s="51" t="str">
         <v>Dorothy Nelson</v>
       </c>
-      <c r="G27" s="53" t="str">
+      <c r="G27" s="52" t="str">
         <v>Sharon Butler</v>
       </c>
     </row>
@@ -59019,7 +55794,7 @@
       <c r="A28" s="14" t="str">
         <v>Daniel King</v>
       </c>
-      <c r="D28" s="52" t="str">
+      <c r="D28" s="51" t="str">
         <v>Arthur Edwards</v>
       </c>
     </row>
@@ -59027,7 +55802,7 @@
       <c r="A29" s="14" t="str">
         <v>Elizabeth Hall</v>
       </c>
-      <c r="D29" s="52" t="str">
+      <c r="D29" s="51" t="str">
         <v>Michelle Rogers</v>
       </c>
     </row>
@@ -59035,7 +55810,7 @@
       <c r="A30" s="14" t="str">
         <v>Maria Garcia</v>
       </c>
-      <c r="D30" s="52" t="str">
+      <c r="D30" s="51" t="str">
         <v>Helen Roberts</v>
       </c>
     </row>
@@ -59043,7 +55818,7 @@
       <c r="A31" s="14" t="str">
         <v>Charles Allen</v>
       </c>
-      <c r="D31" s="52" t="str">
+      <c r="D31" s="51" t="str">
         <v>Harry Morgan</v>
       </c>
     </row>
@@ -59051,7 +55826,7 @@
       <c r="A32" s="14" t="str">
         <v>William White</v>
       </c>
-      <c r="D32" s="52" t="str">
+      <c r="D32" s="51" t="str">
         <v>Sharon Butler</v>
       </c>
     </row>
@@ -59125,7 +55900,7 @@
         <v>Customer_Name</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -59858,11 +56633,11 @@
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="22">
         <f ca="1">TODAY()</f>
-        <v>46172</v>
+        <v>46181</v>
       </c>
       <c r="B3" s="23">
         <f ca="1">NOW()</f>
-        <v>46172.522684606483</v>
+        <v>46181.501241782411</v>
       </c>
       <c r="C3" s="13">
         <f>EOMONTH(Dataset!B2,0)</f>
